--- a/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,42 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Dominio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pregunta_Investigacion</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Objetivo_Experimento</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Variable_Objetivo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Tipo_Problema</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Dominio</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ventana</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Horizonte</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Objetivo</t>
         </is>
       </c>
     </row>
@@ -483,38 +488,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>¿Es posible anticipar el riesgo sanitario del agua mediante información climática e hidrológica?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad del Framework para predecir el IRCA e identificar variables asociadas al riesgo sanitario del agua.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Ejecutado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Evaluar la capacidad del Framework para predecir el riesgo sanitario del agua.</t>
         </is>
       </c>
     </row>
@@ -526,38 +536,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>¿Qué factores permiten anticipar el estado general de la calidad del agua?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad del Framework para predecir la calidad general del recurso hídrico.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>CALIDAD_AGUA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Evaluar el comportamiento general de la calidad del recurso hídrico.</t>
         </is>
       </c>
     </row>
@@ -569,38 +584,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>¿Es posible anticipar la disminución del nivel mínimo del recurso hídrico?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad predictiva del Framework sobre la disponibilidad del recurso hídrico.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Validar la capacidad predictiva sobre la disponibilidad del recurso hídrico.</t>
         </is>
       </c>
     </row>
@@ -612,38 +632,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>¿Qué variables afectan el volumen útil disponible del sistema?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Evaluar la predicción del volumen útil disponible para apoyar la gestión del recurso.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>12</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Validar la predicción del volumen útil disponible.</t>
         </is>
       </c>
     </row>
@@ -655,38 +680,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>¿Es posible anticipar procesos de contaminación orgánica del agua?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Evaluar el comportamiento predictivo de la Demanda Bioquímica de Oxígeno (DBO5).</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>DBO5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>12</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Evaluar contaminación orgánica.</t>
         </is>
       </c>
     </row>
@@ -698,38 +728,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>¿Qué variables explican la contaminación química del recurso hídrico?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Evaluar el comportamiento predictivo de la Demanda Química de Oxígeno (DQO).</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>DQO</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Evaluar contaminación química.</t>
         </is>
       </c>
     </row>
@@ -741,38 +776,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>¿Qué factores afectan el equilibrio ecológico del recurso hídrico?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Evaluar la capacidad del Framework para predecir el Oxígeno Disuelto como indicador ecológico.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Oxigeno_Disuelto</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>12</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Evaluar el estado ecológico del recurso.</t>
         </is>
       </c>
     </row>
@@ -784,38 +824,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>¿Es posible anticipar cambios fisicoquímicos del agua?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Evaluar el comportamiento predictivo del pH como indicador de calidad del agua.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Gestión Hídrica</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>12</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Evaluar el comportamiento fisicoquímico del agua.</t>
         </is>
       </c>
     </row>

--- a/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,16 +16,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +33,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,24 +41,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -429,52 +416,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Experimento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Dominio</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Pregunta_Investigacion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Objetivo_Experimento</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Variable_Objetivo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tipo_Problema</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ventana</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Horizonte</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -668,7 +655,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Ejecutado</t>
         </is>
       </c>
     </row>
@@ -865,6 +852,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,52 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Numero_Predictores</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Registros_Disponibles</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Ventana</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Horizonte</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Umbral_Cobertura_%</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Viabilidad</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Motivo_Viabilidad</t>
         </is>
       </c>
     </row>
@@ -493,12 +523,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>¿Es posible anticipar el riesgo sanitario del agua mediante información climática e hidrológica?</t>
+          <t>¿Es posible anticipar el riesgo sanitario del agua mediante información climática, hidrológica y de infraestructura?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Evaluar la capacidad del Framework para predecir el IRCA e identificar variables asociadas al riesgo sanitario del agua.</t>
+          <t>Evaluar la capacidad del Framework para predecir el IRCA y analizar factores asociados al riesgo sanitario del agua.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -512,19 +542,41 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>528</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Ejecutado</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Viable</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
         </is>
       </c>
     </row>
@@ -551,7 +603,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CALIDAD_AGUA</t>
+          <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -560,19 +612,41 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>96</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>50</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
     </row>
@@ -594,7 +668,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Evaluar la capacidad predictiva del Framework sobre la disponibilidad del recurso hídrico.</t>
+          <t>Evaluar la capacidad predictiva del Framework sobre el nivel mínimo del recurso hídrico.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,19 +682,41 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>87</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
     </row>
@@ -637,12 +733,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>¿Qué variables afectan el volumen útil disponible del sistema?</t>
+          <t>¿Qué variables permiten anticipar el volumen útil disponible del sistema?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Evaluar la predicción del volumen útil disponible para apoyar la gestión del recurso.</t>
+          <t>Evaluar la capacidad del Framework para predecir el volumen útil disponible.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -656,19 +752,41 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>336</v>
+      </c>
+      <c r="I5" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Viable</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
         </is>
       </c>
     </row>
@@ -690,12 +808,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Evaluar el comportamiento predictivo de la Demanda Bioquímica de Oxígeno (DBO5).</t>
+          <t>Evaluar la capacidad predictiva del Framework sobre la Demanda Bioquímica de Oxígeno (DBO5).</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DBO5</t>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -704,19 +822,41 @@
         </is>
       </c>
       <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="J6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
     </row>
@@ -733,17 +873,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>¿Qué variables explican la contaminación química del recurso hídrico?</t>
+          <t>¿Qué variables permiten anticipar la contaminación química del recurso hídrico?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Evaluar el comportamiento predictivo de la Demanda Química de Oxígeno (DQO).</t>
+          <t>Evaluar la capacidad predictiva del Framework sobre la Demanda Química de Oxígeno (DQO).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DQO</t>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -752,19 +892,41 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="J7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>50</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
     </row>
@@ -781,17 +943,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>¿Qué factores afectan el equilibrio ecológico del recurso hídrico?</t>
+          <t>¿Qué factores permiten anticipar cambios en el oxígeno disuelto del recurso hídrico?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Evaluar la capacidad del Framework para predecir el Oxígeno Disuelto como indicador ecológico.</t>
+          <t>Evaluar la capacidad predictiva del Framework sobre el Oxígeno Disuelto (OD).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oxigeno_Disuelto</t>
+          <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -800,19 +962,41 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
     </row>
@@ -829,12 +1013,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>¿Es posible anticipar cambios fisicoquímicos del agua?</t>
+          <t>¿Es posible anticipar cambios en el pH del agua?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evaluar el comportamiento predictivo del pH como indicador de calidad del agua.</t>
+          <t>Evaluar la capacidad predictiva del Framework sobre el pH.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -848,19 +1032,41 @@
         </is>
       </c>
       <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J9" t="n">
         <v>12</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>No viable</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
       </c>
     </row>

--- a/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/catalogo_experimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,55 +456,70 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Variable_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Tipo_Problema</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Numero_Predictores</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Registros_Disponibles</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cobertura_%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Registros_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura_Objetivo_Modelo_%</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ventana</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Horizonte</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Umbral_Cobertura_%</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Viabilidad</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Motivo_Viabilidad</t>
         </is>
@@ -538,43 +553,54 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>9</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>528</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>100</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>528</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>50</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Viable</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
         </is>
@@ -608,43 +634,54 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>10</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>96</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>18.18</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>96</v>
+      </c>
+      <c r="L3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="M3" t="n">
         <v>12</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>50</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
@@ -678,43 +715,54 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>87</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>16.48</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>87</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="M4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>50</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
@@ -748,43 +796,54 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>336</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>63.64</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>336</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="M5" t="n">
         <v>12</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>50</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Viable</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo suficiente para ejecutar el experimento.</t>
         </is>
@@ -818,43 +877,54 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>26</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>4.92</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M6" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>50</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
@@ -888,43 +958,54 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>49</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>49</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="M7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>50</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
@@ -958,43 +1039,54 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>50</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>50</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M8" t="n">
         <v>12</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>50</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
@@ -1028,43 +1120,54 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>10</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>50</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M9" t="n">
         <v>12</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>LSTM</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>50</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>No viable</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Cobertura de la variable objetivo inferior al umbral mínimo del 50%.</t>
         </is>
